--- a/artfynd/A 29884-2025 artfynd.xlsx
+++ b/artfynd/A 29884-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545555</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545557</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545559</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545556</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545560</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1349,8 +1379,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545558</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29884-2025 artfynd.xlsx
+++ b/artfynd/A 29884-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135545555</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135545557</v>
       </c>
       <c r="B3" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135545559</v>
       </c>
       <c r="B4" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>135545560</v>
       </c>
       <c r="B6" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135545558</v>
       </c>
       <c r="B7" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29884-2025 artfynd.xlsx
+++ b/artfynd/A 29884-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135545555</v>
       </c>
       <c r="B2" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135545557</v>
       </c>
       <c r="B3" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135545559</v>
       </c>
       <c r="B4" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>135545560</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135545558</v>
       </c>
       <c r="B7" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29884-2025 artfynd.xlsx
+++ b/artfynd/A 29884-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135545555</v>
       </c>
       <c r="B2" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135545557</v>
       </c>
       <c r="B3" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135545559</v>
       </c>
       <c r="B4" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135545556</v>
       </c>
       <c r="B5" t="n">
-        <v>5497</v>
+        <v>5498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>135545560</v>
       </c>
       <c r="B6" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135545558</v>
       </c>
       <c r="B7" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29884-2025 artfynd.xlsx
+++ b/artfynd/A 29884-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135545555</v>
       </c>
       <c r="B2" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135545557</v>
       </c>
       <c r="B3" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135545559</v>
       </c>
       <c r="B4" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>135545560</v>
       </c>
       <c r="B6" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135545558</v>
       </c>
       <c r="B7" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
